--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freire</t>
   </si>
   <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9105</v>
+        <v>9114</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
@@ -701,7 +701,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9114</v>
+        <v>9105</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:28</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9114</v>
+        <v>9105</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
@@ -701,7 +701,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9105</v>
+        <v>9114</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:22</t>
+    <t xml:space="preserve">2026-09-27 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:11</t>
+    <t xml:space="preserve">2026-10-01 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:52</t>
+    <t xml:space="preserve">2026-10-02 13:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:19</t>
+    <t xml:space="preserve">2026-10-05 07:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
